--- a/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
+++ b/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T10:10:24+00:00</t>
+    <t>2026-04-30T10:17:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
+++ b/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T10:17:38+00:00</t>
+    <t>2026-04-30T10:19:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
+++ b/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T10:19:47+00:00</t>
+    <t>2026-04-30T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
+++ b/conceptmaps-datatypes-part3/ig/CdaADToAddressConceptMap.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T10:20:46+00:00</t>
+    <t>2026-04-30T10:31:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
